--- a/ANALIZAR/convalidaciones.xlsx
+++ b/ANALIZAR/convalidaciones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wild-sis\Desktop\Python Desarrollos\HOJA_DE_RUTA\ANALIZAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wild-sis\Documents\MI REPOSITORIO\HOJA_DE_RUTA\ANALIZAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97D2F75-9CE6-4FC9-B366-F71A59A06F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BAC4D6-DBCD-4ED3-856D-A0EEBEA5D4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-2355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="361">
   <si>
     <t>SIGLA</t>
   </si>
@@ -736,9 +736,6 @@
     <t>CSO454</t>
   </si>
   <si>
-    <t>PSICOLOGÍA DE LAS ORGANIZACIONES</t>
-  </si>
-  <si>
     <t>CSO455</t>
   </si>
   <si>
@@ -1093,15 +1090,6 @@
     <t>ECOLOGÍA SOCIAL</t>
   </si>
   <si>
-    <t>INFORME</t>
-  </si>
-  <si>
-    <t>PRÁCTICAS REALIZADAS EN DIRECCIÓN DE CARRERA E INSTITUCIONES O UNIDADES</t>
-  </si>
-  <si>
-    <t>PRÁCTICAS</t>
-  </si>
-  <si>
     <t>PPP 100</t>
   </si>
   <si>
@@ -1112,6 +1100,9 @@
   </si>
   <si>
     <t>ORDEN</t>
+  </si>
+  <si>
+    <t>PSICOLOGÍA DE LAS ORGANIZACIONES I</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1159,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1211,6 +1202,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFCFCFC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1239,7 +1242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1280,6 +1283,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1517,7 +1535,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="15" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3083,7 +3101,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
+    <row r="65" spans="1:8">
       <c r="B65" s="6" t="s">
         <v>221</v>
       </c>
@@ -3100,38 +3118,39 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
-      <c r="B66" s="6" t="s">
+    <row r="66" spans="1:8" s="24" customFormat="1">
+      <c r="A66" s="18"/>
+      <c r="B66" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E66" s="8" t="s">
+      <c r="D66" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E66" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="F66" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="H66" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8">
+      <c r="H66" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="B67" s="6" t="s">
         <v>227</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>66</v>
+      <c r="D67" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="11"/>
@@ -3140,15 +3159,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
+    <row r="68" spans="1:8">
       <c r="B68" s="6" t="s">
         <v>229</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>66</v>
+      <c r="D68" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="11"/>
@@ -3157,15 +3176,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="2:8">
+    <row r="69" spans="1:8">
       <c r="B69" s="6" t="s">
         <v>231</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>66</v>
+      <c r="D69" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E69" s="11"/>
       <c r="F69" s="11"/>
@@ -3174,38 +3193,39 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="2:8">
-      <c r="B70" s="6" t="s">
+    <row r="70" spans="1:8" s="24" customFormat="1">
+      <c r="A70" s="18"/>
+      <c r="B70" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E70" s="8" t="s">
+      <c r="D70" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E70" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="F70" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="H70" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8">
+      <c r="H70" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="B71" s="6" t="s">
         <v>237</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>66</v>
+        <v>360</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="11"/>
@@ -3214,15 +3234,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="2:8">
+    <row r="72" spans="1:8">
       <c r="B72" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C72" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="C72" s="14" t="s">
-        <v>240</v>
-      </c>
       <c r="D72" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
@@ -3231,15 +3251,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="2:8">
+    <row r="73" spans="1:8">
       <c r="B73" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C73" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="C73" s="14" t="s">
-        <v>242</v>
-      </c>
       <c r="D73" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
@@ -3248,15 +3268,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="2:8">
+    <row r="74" spans="1:8">
       <c r="B74" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="C74" s="14" t="s">
-        <v>244</v>
-      </c>
       <c r="D74" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="11"/>
@@ -3265,38 +3285,39 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="2:8">
-      <c r="B75" s="6" t="s">
+    <row r="75" spans="1:8" s="24" customFormat="1">
+      <c r="A75" s="18"/>
+      <c r="B75" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C75" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="D75" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E75" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="D75" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E75" s="8" t="s">
+      <c r="F75" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="G75" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H75" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="B76" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="G75" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8">
-      <c r="B76" s="6" t="s">
+      <c r="C76" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C76" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>66</v>
+      <c r="D76" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="11"/>
@@ -3305,15 +3326,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="2:8">
+    <row r="77" spans="1:8">
       <c r="B77" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C77" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="C77" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>66</v>
+      <c r="D77" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E77" s="11"/>
       <c r="F77" s="11"/>
@@ -3322,15 +3343,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="2:8">
+    <row r="78" spans="1:8">
       <c r="B78" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C78" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="C78" s="14" t="s">
-        <v>254</v>
-      </c>
       <c r="D78" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="11"/>
@@ -3339,15 +3360,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="2:8">
+    <row r="79" spans="1:8">
       <c r="B79" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C79" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="C79" s="14" t="s">
-        <v>256</v>
-      </c>
       <c r="D79" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E79" s="11"/>
       <c r="F79" s="11"/>
@@ -3356,15 +3377,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="2:8">
+    <row r="80" spans="1:8">
       <c r="B80" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C80" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="C80" s="14" t="s">
-        <v>258</v>
-      </c>
       <c r="D80" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="11"/>
@@ -3373,38 +3394,39 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
-      <c r="B81" s="6" t="s">
+    <row r="81" spans="1:8" s="24" customFormat="1">
+      <c r="A81" s="18"/>
+      <c r="B81" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E81" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="C81" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E81" s="8" t="s">
+      <c r="F81" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="F81" s="9" t="s">
+      <c r="G81" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H81" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="B82" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="G81" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8">
-      <c r="B82" s="6" t="s">
-        <v>262</v>
-      </c>
       <c r="C82" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>66</v>
+        <v>249</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="11"/>
@@ -3413,15 +3435,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="2:8">
+    <row r="83" spans="1:8">
       <c r="B83" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C83" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C83" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>66</v>
+      <c r="D83" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
@@ -3430,38 +3452,39 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
-      <c r="B84" s="6" t="s">
+    <row r="84" spans="1:8" s="24" customFormat="1">
+      <c r="A84" s="18"/>
+      <c r="B84" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C84" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E84" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C84" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E84" s="8" t="s">
+      <c r="F84" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="F84" s="9" t="s">
+      <c r="G84" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H84" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="B85" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="G84" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8">
-      <c r="B85" s="6" t="s">
-        <v>268</v>
-      </c>
       <c r="C85" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E85" s="11"/>
       <c r="F85" s="11"/>
@@ -3470,15 +3493,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="1:8">
       <c r="B86" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="11"/>
@@ -3487,38 +3510,39 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="2:8">
-      <c r="B87" s="6" t="s">
+    <row r="87" spans="1:8" s="24" customFormat="1">
+      <c r="A87" s="18"/>
+      <c r="B87" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E87" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="C87" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E87" s="8" t="s">
+      <c r="F87" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="F87" s="9" t="s">
+      <c r="G87" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H87" s="23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="B88" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="G87" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
-      <c r="B88" s="6" t="s">
-        <v>273</v>
-      </c>
       <c r="C88" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>66</v>
+        <v>249</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="11"/>
@@ -3527,15 +3551,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:8">
+    <row r="89" spans="1:8">
       <c r="B89" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>66</v>
+        <v>263</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="E89" s="11"/>
       <c r="F89" s="11"/>
@@ -3544,15 +3568,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="1:8">
       <c r="B90" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="11"/>
@@ -3561,15 +3585,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="1:8">
       <c r="B91" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E91" s="11"/>
       <c r="F91" s="11"/>
@@ -3578,15 +3602,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="1:8">
       <c r="B92" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="11"/>
@@ -3595,15 +3619,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="2:8">
+    <row r="93" spans="1:8">
       <c r="B93" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C93" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="C93" s="14" t="s">
-        <v>279</v>
-      </c>
       <c r="D93" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="11"/>
@@ -3612,15 +3636,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="2:8">
+    <row r="94" spans="1:8">
       <c r="B94" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C94" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="C94" s="14" t="s">
-        <v>281</v>
-      </c>
       <c r="D94" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E94" s="11"/>
       <c r="F94" s="11"/>
@@ -3629,15 +3653,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="2:8">
+    <row r="95" spans="1:8">
       <c r="B95" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C95" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C95" s="14" t="s">
-        <v>283</v>
-      </c>
       <c r="D95" s="6" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="E95" s="11"/>
       <c r="F95" s="11"/>
@@ -3646,15 +3670,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="1:8">
       <c r="B96" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C96" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="D96" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="11"/>
@@ -3665,13 +3689,13 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C97" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C97" s="7" t="s">
-        <v>288</v>
-      </c>
       <c r="D97" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E97" s="11"/>
       <c r="F97" s="11"/>
@@ -3682,13 +3706,13 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C98" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C98" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="D98" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="11"/>
@@ -3699,13 +3723,13 @@
     </row>
     <row r="99" spans="2:8">
       <c r="B99" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C99" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C99" s="7" t="s">
-        <v>292</v>
-      </c>
       <c r="D99" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E99" s="11"/>
       <c r="F99" s="11"/>
@@ -3716,19 +3740,19 @@
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C100" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="D100" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E100" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="D100" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E100" s="8" t="s">
+      <c r="F100" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>66</v>
@@ -3739,13 +3763,13 @@
     </row>
     <row r="101" spans="2:8">
       <c r="B101" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C101" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C101" s="7" t="s">
-        <v>298</v>
-      </c>
       <c r="D101" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E101" s="11"/>
       <c r="F101" s="11"/>
@@ -3756,13 +3780,13 @@
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="C102" s="7" t="s">
-        <v>300</v>
-      </c>
       <c r="D102" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="11"/>
@@ -3773,19 +3797,19 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C103" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="D103" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E103" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D103" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E103" s="8" t="s">
+      <c r="F103" s="9" t="s">
         <v>303</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>304</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>175</v>
@@ -3796,13 +3820,13 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C104" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C104" s="7" t="s">
-        <v>306</v>
-      </c>
       <c r="D104" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="11"/>
@@ -3813,13 +3837,13 @@
     </row>
     <row r="105" spans="2:8">
       <c r="B105" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C105" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="C105" s="7" t="s">
-        <v>308</v>
-      </c>
       <c r="D105" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E105" s="11"/>
       <c r="F105" s="11"/>
@@ -3830,13 +3854,13 @@
     </row>
     <row r="106" spans="2:8">
       <c r="B106" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C106" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C106" s="7" t="s">
-        <v>310</v>
-      </c>
       <c r="D106" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="11"/>
@@ -3847,19 +3871,19 @@
     </row>
     <row r="107" spans="2:8">
       <c r="B107" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="D107" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E107" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="D107" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E107" s="8" t="s">
+      <c r="F107" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>314</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>47</v>
@@ -3870,13 +3894,13 @@
     </row>
     <row r="108" spans="2:8">
       <c r="B108" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C108" s="7" t="s">
-        <v>316</v>
-      </c>
       <c r="D108" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="11"/>
@@ -3887,13 +3911,13 @@
     </row>
     <row r="109" spans="2:8">
       <c r="B109" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C109" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C109" s="7" t="s">
-        <v>318</v>
-      </c>
       <c r="D109" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E109" s="11"/>
       <c r="F109" s="11"/>
@@ -3904,13 +3928,13 @@
     </row>
     <row r="110" spans="2:8">
       <c r="B110" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="C110" s="7" t="s">
-        <v>320</v>
-      </c>
       <c r="D110" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="11"/>
@@ -3921,19 +3945,19 @@
     </row>
     <row r="111" spans="2:8">
       <c r="B111" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C111" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="D111" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E111" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="D111" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E111" s="8" t="s">
+      <c r="F111" s="9" t="s">
         <v>323</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>324</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>47</v>
@@ -3944,13 +3968,13 @@
     </row>
     <row r="112" spans="2:8">
       <c r="B112" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C112" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C112" s="7" t="s">
-        <v>326</v>
-      </c>
       <c r="D112" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E112" s="11"/>
       <c r="F112" s="11"/>
@@ -3961,13 +3985,13 @@
     </row>
     <row r="113" spans="2:8">
       <c r="B113" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C113" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C113" s="7" t="s">
-        <v>328</v>
-      </c>
       <c r="D113" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E113" s="11"/>
       <c r="F113" s="11"/>
@@ -3978,13 +4002,13 @@
     </row>
     <row r="114" spans="2:8">
       <c r="B114" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C114" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C114" s="7" t="s">
-        <v>330</v>
-      </c>
       <c r="D114" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="11"/>
@@ -3995,13 +4019,13 @@
     </row>
     <row r="115" spans="2:8">
       <c r="B115" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C115" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="C115" s="7" t="s">
-        <v>332</v>
-      </c>
       <c r="D115" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E115" s="11"/>
       <c r="F115" s="11"/>
@@ -4012,13 +4036,13 @@
     </row>
     <row r="116" spans="2:8">
       <c r="B116" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C116" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C116" s="7" t="s">
-        <v>334</v>
-      </c>
       <c r="D116" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="11"/>
@@ -4029,13 +4053,13 @@
     </row>
     <row r="117" spans="2:8">
       <c r="B117" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C117" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="C117" s="7" t="s">
-        <v>336</v>
-      </c>
       <c r="D117" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E117" s="11"/>
       <c r="F117" s="11"/>
@@ -4046,19 +4070,19 @@
     </row>
     <row r="118" spans="2:8">
       <c r="B118" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C118" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="D118" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E118" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="D118" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>339</v>
-      </c>
       <c r="F118" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G118" s="8" t="s">
         <v>66</v>
@@ -4069,13 +4093,13 @@
     </row>
     <row r="119" spans="2:8">
       <c r="B119" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C119" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="C119" s="7" t="s">
-        <v>341</v>
-      </c>
       <c r="D119" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E119" s="11"/>
       <c r="F119" s="11"/>
@@ -4086,19 +4110,19 @@
     </row>
     <row r="120" spans="2:8">
       <c r="B120" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C120" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C120" s="7" t="s">
+      <c r="D120" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E120" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="D120" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>344</v>
-      </c>
       <c r="F120" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>66</v>
@@ -4109,13 +4133,13 @@
     </row>
     <row r="121" spans="2:8">
       <c r="B121" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C121" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C121" s="7" t="s">
-        <v>346</v>
-      </c>
       <c r="D121" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E121" s="11"/>
       <c r="F121" s="11"/>
@@ -4126,13 +4150,13 @@
     </row>
     <row r="122" spans="2:8">
       <c r="B122" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C122" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="C122" s="7" t="s">
-        <v>348</v>
-      </c>
       <c r="D122" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E122" s="11"/>
       <c r="F122" s="11"/>
@@ -4143,19 +4167,19 @@
     </row>
     <row r="123" spans="2:8">
       <c r="B123" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C123" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="C123" s="7" t="s">
+      <c r="D123" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E123" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="D123" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E123" s="8" t="s">
+      <c r="F123" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>352</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>66</v>
@@ -4166,13 +4190,13 @@
     </row>
     <row r="124" spans="2:8">
       <c r="B124" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C124" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="C124" s="7" t="s">
-        <v>354</v>
-      </c>
       <c r="D124" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E124" s="11"/>
       <c r="F124" s="11"/>
@@ -4183,13 +4207,13 @@
     </row>
     <row r="125" spans="2:8">
       <c r="B125" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C125" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C125" s="7" t="s">
-        <v>356</v>
-      </c>
       <c r="D125" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E125" s="11"/>
       <c r="F125" s="11"/>
@@ -4199,26 +4223,20 @@
       </c>
     </row>
     <row r="126" spans="2:8">
-      <c r="B126" s="6" t="s">
+      <c r="B126" s="6"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F126" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="F126" s="9" t="s">
-        <v>361</v>
       </c>
       <c r="G126" s="8" t="s">
         <v>175</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
